--- a/static/downloads/budzet-projekta-sablon.xlsx
+++ b/static/downloads/budzet-projekta-sablon.xlsx
@@ -2,23 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="495" yWindow="2040" windowWidth="21600" windowHeight="11385" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Budžet Projekta" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Uputstvo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;RSD&quot;"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0\ &quot;RSD&quot;_-;\-* #,##0\ &quot;RSD&quot;_-;_-* &quot;-&quot;\ &quot;RSD&quot;_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00 &quot;RSD&quot;"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,24 +30,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF006AAF"/>
+      <sz val="14"/>
+    </font>
+    <font>
       <name val="Helvetica Neue"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <family val="2"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
-      <b val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00006AAF"/>
-      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
@@ -56,18 +73,23 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00006AAF"/>
-        <bgColor rgb="00006AAF"/>
+        <fgColor rgb="FF006AAF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6451F"/>
-        <bgColor rgb="00C6451F"/>
+        <fgColor rgb="FFC6451F"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -77,35 +99,102 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FFC6C6C6"/>
       </left>
       <right style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FFC6C6C6"/>
       </right>
       <top style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FFC6C6C6"/>
       </top>
       <bottom style="thin">
-        <color rgb="00000000"/>
+        <color rgb="FFC6C6C6"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="3" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Currency [0]" xfId="1" builtinId="7"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -254,6 +343,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -288,6 +378,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -311,7 +402,6 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -322,31 +412,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -368,7 +458,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -426,7 +516,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -439,13 +529,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -465,403 +554,397 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="25" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="30" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="12" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="20" bestFit="1" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="32.25" customFormat="1" customHeight="1" s="2">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>Kategorija Troškova</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>Opis</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>Jedinična Cena (RSD)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>Količina</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>Ukupno (RSD)</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Plate i naknade</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="11" t="inlineStr">
         <is>
           <t>Plata koordinatora projekta (6 meseci)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="12" t="n">
         <v>50000</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="14">
         <f>C2*D2</f>
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Plate i naknade</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>Materijalni troškovi</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Honorar volontera</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="13" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="14">
         <f>C3*D3</f>
         <v/>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Materijalni troškovi</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>Usluge</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>Kancelarijski materijal</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="14">
         <f>C4*D4</f>
         <v/>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Materijalni troškovi</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Štampanje materijala</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="12" t="n">
         <v>15000</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="14">
         <f>C5*D5</f>
         <v/>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Usluge</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Iznajmljivanje sale za radionicu</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="12" t="n">
         <v>8000</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="14">
         <f>C6*D6</f>
         <v/>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Usluge</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Internet i komunikacije</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="12" t="n">
         <v>3000</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="13" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="14">
         <f>C7*D7</f>
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="8" ht="19.5" customHeight="1">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Ostalo</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Nepredviđeni troškovi (max 10%)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="14">
         <f>C8*D8</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="21.75" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>UKUPNO</t>
         </is>
       </c>
-      <c r="E9" s="5">
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="18">
         <f>SUM(E2:E8)</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <dataValidations count="1">
-    <dataValidation sqref="C2:D8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Nevalidna vrednost" error="Molimo unesite pozitivan broj" type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="C2:C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Nevalidna vrednost" error="Molimo unesite pozitivan broj" type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="80" customWidth="1" min="1" max="1"/>
+    <col width="80" bestFit="1" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>UPUTSTVO ZA POPUNJAVANJE BUDŽETA PROJEKTA</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
-    <row r="3">
+    <row r="2" ht="18.75" customHeight="1"/>
+    <row r="3" ht="18.75" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
           <t>Koraci za popunjavanje:</t>
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="18.75" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
           <t>1. Preuzmite Excel šablon sa DOMOVIK platforme</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="18.75" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>2. Popunite tabelu sa troškovima vašeg projekta</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="18.75" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
           <t>3. Sačuvajte fajl i upload-ujte nazad na platformu</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
-    <row r="8">
+    <row r="7" ht="18.75" customHeight="1"/>
+    <row r="8" ht="18.75" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
           <t>Kolone u tabeli:</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="18.75" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>• Kategorija Troškova - Izaberite kategoriju (Plate, Materijalni troškovi, Usluge, Ostalo)</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="18.75" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
           <t>• Opis - Detaljan opis troška (npr. 'Plata koordinatora projekta za 6 meseci')</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="18.75" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
           <t>• Jedinična Cena (RSD) - Cena po jedinici u dinarima</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="18.75" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
           <t>• Količina - Broj jedinica (npr. broj meseci, broj ljudi, itd.)</t>
         </is>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="18.75" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
           <t>• Ukupno (RSD) - Automatski izračunato (ne menjajte formulu!)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr"/>
-    </row>
-    <row r="15">
+    <row r="14" ht="18.75" customHeight="1"/>
+    <row r="15" ht="18.75" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
           <t>VAŽNO:</t>
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="18.75" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>✓ Kolona 'Ukupno' se automatski računa - ne menjajte formule</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="18.75" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
           <t>✓ Unesite sve troškove koji su relevantni za vaš projekat</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18.75" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
           <t>✓ Ukupan budžet se prikazuje na dnu tabele</t>
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="18.75" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
           <t>✓ Maksimalno 10% budžeta može biti u kategoriji 'Nepredviđeni troškovi'</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-    </row>
-    <row r="21">
+    <row r="20" ht="18.75" customHeight="1"/>
+    <row r="21" ht="18.75" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
           <t>Primer popunjene stavke:</t>
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="18.75" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
           <t>Kategorija: Materijalni troškovi</t>
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="18.75" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
           <t>Opis: Štampanje 500 flajera za promociju projekta</t>
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="18.75" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
           <t>Jedinična Cena: 10 RSD</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="18.75" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
           <t>Količina: 500</t>
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="18.75" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
           <t>Ukupno: 5,000 RSD (automatski izračunato)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
-    <row r="28">
+    <row r="27" ht="18.75" customHeight="1"/>
+    <row r="28" ht="18.75" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
           <t>Za pomoć kontaktirajte: domovik@example.com</t>
@@ -869,6 +952,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>